--- a/PBS_MASTER_CANONICAL.xlsx
+++ b/PBS_MASTER_CANONICAL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -754,47 +754,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3.3</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sistem Feeding / Charging</t>
+          <t>Motor Screw Hopper Elektroda Tanur</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hoist Crane</t>
+          <t>Sistem Feeding / Charging</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -807,54 +807,54 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hopper</t>
+          <t>Hoist Crane</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sistem Daya Tanur</t>
+          <t>Hopper</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Trafo Step Down Tanur</t>
+          <t>Sistem Daya Tanur</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -867,14 +867,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cubicle Sistem Daya Tanur</t>
+          <t>Trafo Step Down Tanur</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -887,54 +887,54 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Busbar / Bus Tube / Flexible Cable</t>
+          <t>Cubicle Sistem Daya Tanur</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sistem Kontrol dan Instrumentasi</t>
+          <t>Busbar / Bus Tube / Flexible Cable</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1.6.1</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Panel Consule Control</t>
+          <t>Sistem Kontrol dan Instrumentasi</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1.6.2</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -947,14 +947,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thermocouple</t>
+          <t>Panel Consule Control</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1.6.3</t>
+          <t>1.6.2</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -967,54 +967,54 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Panel Temperatur Tanur</t>
+          <t>Thermocouple</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6.3</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sistem Pendinginan Air</t>
+          <t>Panel Temperatur Tanur</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1.7.1</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Water Jacket</t>
+          <t>Sistem Pendinginan Air</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1.7.2</t>
+          <t>1.7.1</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1027,14 +1027,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Water Box</t>
+          <t>Water Jacket</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1.7.3</t>
+          <t>1.7.2</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1047,54 +1047,54 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pompa sirkulasi</t>
+          <t>Water Box</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7.3</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sistem Udara Bertekanan dan Sirkulasi Udara</t>
+          <t>Pompa sirkulasi</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1.8.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pneumatic system</t>
+          <t>Sistem Udara Bertekanan dan Sirkulasi Udara</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1.8.2</t>
+          <t>1.8.1</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1107,54 +1107,54 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Blower Tiup</t>
+          <t>Pneumatic system</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8.2</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sistem Tapping Logam dan Slag</t>
+          <t>Blower Tiup</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1.9.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Peralatan Pembukaan dan Penutupan Taphole</t>
+          <t>Sistem Tapping Logam dan Slag</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1.9.2</t>
+          <t>1.9.1</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1167,54 +1167,54 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tapping Launder / Spout</t>
+          <t>Peralatan Pembukaan dan Penutupan Taphole</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.9.2</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sistem Penanganan Logam dan Slag Cair</t>
+          <t>Tapping Launder / Spout</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1.10.1</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Prisma Pot</t>
+          <t>Sistem Penanganan Logam dan Slag Cair</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1.10.2</t>
+          <t>1.10.1</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1227,74 +1227,74 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Slag Caster</t>
+          <t>Prisma Pot</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.10.2</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Area Pemurnian</t>
+          <t>Slag Caster</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sistem Refining Pot, Pengadukan, dan Transfer Timah</t>
+          <t>Area Pemurnian</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ketel</t>
+          <t>Sistem Refining Pot, Pengadukan, dan Transfer Timah</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1307,14 +1307,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Inverter Control Motor Mixer Refining</t>
+          <t>Ketel</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Dudukan Mixer Pot Refining</t>
+          <t>Inverter Control Motor Mixer Refining</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2.1.4</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1347,14 +1347,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pompa Timah Refining</t>
+          <t>Dudukan Mixer Pot Refining</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2.1.5</t>
+          <t>2.1.4</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1367,14 +1367,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pompa Timah</t>
+          <t>Pompa Timah Refining</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2.1.6</t>
+          <t>2.1.5</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1387,14 +1387,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mixer / Agitator Pot Refining (motor, shaft, dan impeller)</t>
+          <t>Pompa Timah</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2.1.7</t>
+          <t>2.1.6</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1407,14 +1407,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Peralatan Skimming / Pengeluaran Dross</t>
+          <t>Mixer / Agitator Pot Refining (motor, shaft, dan impeller)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2.1.8</t>
+          <t>2.1.7</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1427,54 +1427,54 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wadah Dross / Residu Refining</t>
+          <t>Peralatan Skimming / Pengeluaran Dross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1.8</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sistem Crystallizer</t>
+          <t>Wadah Dross / Residu Refining</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pot Crystallizer</t>
+          <t>Sistem Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1487,14 +1487,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Motor Gearbox Crystallizer</t>
+          <t>Pot Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1507,54 +1507,54 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Motor Gearbox Screw Crystallizer</t>
+          <t>Motor Gearbox Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sistem Casting dan Pembentukan Ingot</t>
+          <t>Motor Gearbox Screw Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2.3.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wadah Cetak Ingot</t>
+          <t>Sistem Casting dan Pembentukan Ingot</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>2.3.1</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1567,14 +1567,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Control Heater Spiral Talang Casting</t>
+          <t>Wadah Cetak Ingot</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2.3.3</t>
+          <t>2.3.2</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Control Heater Spiral Pot Casting</t>
+          <t>Control Heater Spiral Talang Casting</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2.3.4</t>
+          <t>2.3.3</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1607,14 +1607,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Element Pemanas Talang Casting</t>
+          <t>Control Heater Spiral Pot Casting</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2.3.5</t>
+          <t>2.3.4</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1627,14 +1627,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Talang Casting</t>
+          <t>Element Pemanas Talang Casting</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2.3.6</t>
+          <t>2.3.5</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1647,54 +1647,54 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Pot Casting / Holding Kettle</t>
+          <t>Talang Casting</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3.6</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sistem Pemanasan dan Burner</t>
+          <t>Pot Casting / Holding Kettle</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Electrical Burner – Refining</t>
+          <t>Sistem Pemanasan dan Burner</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Electrical Burner – Crystallizer</t>
+          <t>Electrical Burner – Refining</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2.4.3</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1727,54 +1727,54 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Burner – Flame Oven</t>
+          <t>Electrical Burner – Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4.3</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sistem Gas Handling, Ventilasi, dan Dust Collection</t>
+          <t>Burner – Flame Oven</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2.5.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Inverter Control Blower Hisap Bag House Refining</t>
+          <t>Sistem Gas Handling, Ventilasi, dan Dust Collection</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>2.5.1</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1787,14 +1787,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Blower Tiup – Refining</t>
+          <t>Inverter Control Blower Hisap Bag House Refining</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2.5.3</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1807,14 +1807,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Panel Control Pneumatic Bag House Refining</t>
+          <t>Blower Tiup – Refining</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2.5.4</t>
+          <t>2.5.3</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Pneumatic System Refining</t>
+          <t>Panel Control Pneumatic Bag House Refining</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2.5.5</t>
+          <t>2.5.4</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Bag House Refining</t>
+          <t>Pneumatic System Refining</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2.5.6</t>
+          <t>2.5.5</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1867,14 +1867,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Blower Hisap Bag House Refining</t>
+          <t>Bag House Refining</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2.5.7</t>
+          <t>2.5.6</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1887,14 +1887,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Inverter Control Blower Hisap Bag House Crystallizer</t>
+          <t>Blower Hisap Bag House Refining</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2.5.8</t>
+          <t>2.5.7</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1907,14 +1907,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Blower Tiup – Crystallizer</t>
+          <t>Inverter Control Blower Hisap Bag House Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2.5.9</t>
+          <t>2.5.8</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1927,14 +1927,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Blower Hisap Bag House Crystallizer</t>
+          <t>Blower Tiup – Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2.5.10</t>
+          <t>2.5.9</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1947,14 +1947,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Panel Control Pneumatic Bag House Crystallizer</t>
+          <t>Blower Hisap Bag House Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2.5.11</t>
+          <t>2.5.10</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1967,14 +1967,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Bag House Flame Oven</t>
+          <t>Panel Control Pneumatic Bag House Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2.5.12</t>
+          <t>2.5.11</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pneumatic Flame Oven</t>
+          <t>Bag House Flame Oven</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2.5.13</t>
+          <t>2.5.12</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2007,14 +2007,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Blower Hisap Flame Oven</t>
+          <t>Pneumatic Flame Oven</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2.5.14</t>
+          <t>2.5.13</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2027,14 +2027,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Hood dan Ducting Penangkap Fume</t>
+          <t>Blower Hisap Flame Oven</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2.5.15</t>
+          <t>2.5.14</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2047,14 +2047,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Stack / Cerobong</t>
+          <t>Hood dan Ducting Penangkap Fume</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2.5.16</t>
+          <t>2.5.15</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2067,34 +2067,34 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cyclone - Pemurnian</t>
+          <t>Stack / Cerobong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5.16</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sistem Pendinginan Air</t>
+          <t>Cyclone - Pemurnian</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2.6.1</t>
+          <t>2.5.17</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Pompa Air Pendingin Pot Casting</t>
+          <t>ID Fan</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2.6.2</t>
+          <t>2.5.18</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2127,34 +2127,34 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tower Tandon Air – Refining/Casting</t>
+          <t>Exhaust Fan</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2.6.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sirkulasi Air</t>
+          <t>Sistem Pendinginan Air</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2.6.4</t>
+          <t>2.6.1</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2167,14 +2167,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tower Tandon Air – Crystallizer</t>
+          <t>Pompa Air Pendingin Pot Casting</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2.6.5</t>
+          <t>2.6.2</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2187,34 +2187,34 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mesin Pompa Air Pendingin Crystallizer &amp; Casting</t>
+          <t>Tower Tandon Air – Refining/Casting</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6.3</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sistem Kelistrikan, Kontrol, Instrumentasi, dan Interlock</t>
+          <t>Sirkulasi Air</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2.7.1</t>
+          <t>2.6.4</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Panel Electrical Refining</t>
+          <t>Tower Tandon Air – Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2.7.2</t>
+          <t>2.6.5</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2247,14 +2247,14 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Panel Thermocouple Pot Refining</t>
+          <t>Mesin Pompa Air Pendingin Crystallizer &amp; Casting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2.7.3</t>
+          <t>2.6.6</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2267,14 +2267,14 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Panel Electrical Crystallizer</t>
+          <t>Water Instalasi</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2.7.4</t>
+          <t>2.6.7</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Panel Electrical Casting</t>
+          <t>Water Circulation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2307,14 +2307,14 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sistem Pengangkatan, Platform, dan Akses</t>
+          <t>Sistem Kelistrikan, Kontrol, Instrumentasi, dan Interlock</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2.8.1</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2327,14 +2327,14 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Hoist Crane – Refining</t>
+          <t>Panel Electrical Refining</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2.8.2</t>
+          <t>2.7.2</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2347,14 +2347,14 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Lantai Atas Refining</t>
+          <t>Panel Thermocouple Pot Refining</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2.8.3</t>
+          <t>2.7.3</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Hoist Crane – Crystallizer</t>
+          <t>Panel Electrical Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2.8.4</t>
+          <t>2.7.4</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2387,34 +2387,34 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Hoist Crane – Casting</t>
+          <t>Panel Electrical Casting</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2.8.5</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Hoist Crane – Composisi</t>
+          <t>Sistem Pengangkatan, Platform, dan Akses</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2.8.6</t>
+          <t>2.8.1</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2427,14 +2427,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Hoist Crane – Antrasite</t>
+          <t>Hoist Crane – Refining</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2.8.7</t>
+          <t>2.8.2</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2447,14 +2447,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Hoist Crane – Gudang Ingot</t>
+          <t>Lantai Atas Refining</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2.8.8</t>
+          <t>2.8.3</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2467,34 +2467,34 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Hoist Crane – Granular</t>
+          <t>Hoist Crane – Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.8.4</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Persiapan Komposisi / Bahan Tambahan</t>
+          <t>Hoist Crane – Casting</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2.9.1</t>
+          <t>2.8.5</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2507,34 +2507,34 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Hoist Crane – Composisi</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.8.6</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Persiapan Antrasit</t>
+          <t>Hoist Crane – Antrasite</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2.10.1</t>
+          <t>2.8.7</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2547,54 +2547,54 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mesin Crusher</t>
+          <t>Hoist Crane – Gudang Ingot</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.8.8</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Sistem Granular / Pengolahan Material Recycle</t>
+          <t>Hoist Crane – Granular</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2.11.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Persiapan Komposisi / Bahan Tambahan</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2.11.2</t>
+          <t>2.9.1</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2607,14 +2607,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Motor Gearbox Mixer</t>
+          <t>Mixer</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2627,14 +2627,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sistem Flame Oven</t>
+          <t>Persiapan Antrasit</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2.12.1</t>
+          <t>2.10.1</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2647,54 +2647,54 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Tanur Flame Oven</t>
+          <t>Mesin Crusher</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2.12.2</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Prisma Pot</t>
+          <t>Sistem Granular / Pengolahan Material Recycle</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.11.1</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Gudang dan Penimbangan Ingot</t>
+          <t>Mixer</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2.13.1</t>
+          <t>2.11.2</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2707,34 +2707,34 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Timbangan Duduk</t>
+          <t>Motor Gearbox Mixer</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2.13.2</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Anak Timbangan</t>
+          <t>Sistem Flame Oven</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2.13.3</t>
+          <t>2.12.1</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2747,14 +2747,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Sampler</t>
+          <t>Tanur Flame Oven</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2.13.4</t>
+          <t>2.12.2</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2767,54 +2767,54 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Separator</t>
+          <t>Prisma Pot</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Utilitas Pabrik</t>
+          <t>Gudang dan Penimbangan Ingot</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.13.1</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sistem Kelistrikan Utama dan Daya Cadangan</t>
+          <t>Timbangan Duduk</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3.1.1</t>
+          <t>2.13.2</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2827,14 +2827,14 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Kubikel Incoming PLN</t>
+          <t>Anak Timbangan</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>2.13.3</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2847,14 +2847,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Genset</t>
+          <t>Sampler</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3.1.3</t>
+          <t>2.13.4</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2867,54 +2867,54 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Panel Kubikel dan DSI</t>
+          <t>Separator</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3.1.4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Panel Main Switch Board</t>
+          <t>Utilitas Pabrik</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3.1.5</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Panel Sinkron Genset</t>
+          <t>Sistem Kelistrikan Utama dan Daya Cadangan</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3.1.6</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Panel Kapasitor Bank</t>
+          <t>Kubikel Incoming PLN</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3.1.7</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2947,14 +2947,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Incoming Power Feeder</t>
+          <t>Genset</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3.1.8</t>
+          <t>3.1.3</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2967,14 +2967,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Main Power Transformer</t>
+          <t>Panel Kubikel dan DSI</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3.1.9</t>
+          <t>3.1.4</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2987,14 +2987,14 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sistem Grounding</t>
+          <t>Panel Main Switch Board</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3.1.10</t>
+          <t>3.1.5</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3007,34 +3007,34 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sistem Proteksi Petir</t>
+          <t>Panel Sinkron Genset</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1.6</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Sistem Udara Bertekanan Pabrik</t>
+          <t>Panel Kapasitor Bank</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>3.1.7</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3047,14 +3047,14 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Kompresor Listrik</t>
+          <t>Incoming Power Feeder</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.1.8</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3067,34 +3067,34 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Tangki Kompresor</t>
+          <t>Main Power Transformer</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1.9</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mesin Perkakas</t>
+          <t>Sistem Grounding</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3.3.1</t>
+          <t>3.1.10</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3107,14 +3107,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mesin Skrap</t>
+          <t>Sistem Proteksi Petir</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3.3.2</t>
+          <t>3.1.11</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3127,14 +3127,14 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mesin Milling</t>
+          <t>Panel Battery</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3.3.3</t>
+          <t>3.1.12</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Mesin Roll</t>
+          <t>Panel Furnace Tegangan Rendah</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3.3.4</t>
+          <t>3.1.13</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3167,14 +3167,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mesin Press</t>
+          <t>Distribution Board</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3.3.5</t>
+          <t>3.1.14</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3187,14 +3187,14 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mesin Las</t>
+          <t>Trafo Step Up 20 kV</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3.3.6</t>
+          <t>3.1.15</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3207,54 +3207,54 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Mesin Potong</t>
+          <t>Ruang Trafo</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3.3.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Mesin Bubut</t>
+          <t>Sistem Udara Bertekanan Pabrik</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sistem Bahan Bakar</t>
+          <t>Kompresor Listrik</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3.4.1</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3267,14 +3267,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Pompa BBM</t>
+          <t>Tangki Kompresor</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3287,14 +3287,14 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Jockey Pump</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3307,54 +3307,54 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Tangki BBM</t>
+          <t>Mesin Compressor Sullair</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Peralatan Pemindah Material</t>
+          <t>Pneumatic System</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3.5.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Forklift</t>
+          <t>Mesin Perkakas</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3.5.2</t>
+          <t>3.3.1</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3367,34 +3367,34 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Conveyor</t>
+          <t>Mesin Skrap</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Struktur Sipil</t>
+          <t>Mesin Milling</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3.6.1</t>
+          <t>3.3.3</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Platform kerja</t>
+          <t>Mesin Roll</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3.6.2</t>
+          <t>3.3.4</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3427,14 +3427,14 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Railing</t>
+          <t>Mesin Press</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3.6.3</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3447,14 +3447,14 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Tangga</t>
+          <t>Mesin Las</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3.6.4</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3467,14 +3467,14 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Atap</t>
+          <t>Mesin Potong</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3.6.5</t>
+          <t>3.3.7</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3487,14 +3487,14 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Dinding</t>
+          <t>Mesin Bubut</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3507,14 +3507,14 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Sistem Proteksi Kebakaran</t>
+          <t>Sistem Bahan Bakar</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3.7.1</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3527,34 +3527,34 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Pompa Hydrant / Fire Pump</t>
+          <t>Pompa BBM</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Perkakas dan Alat Ukur Workshop</t>
+          <t>Filter</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3.8.1</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3567,94 +3567,94 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Lifting Tools / Peralatan Alat Berat Workshop</t>
+          <t>Tangki BBM</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3.8.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Alat Ukur Maintenance / Peralatan Kelistrikan Workshop</t>
+          <t>Peralatan Pemindah Material</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5.1</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Area Peleburan Sekunder / Dust Recovery</t>
+          <t>Forklift</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.5.2</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sistem Penerimaan, Penyimpanan, dan Pelletizing</t>
+          <t>Conveyor</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Dust Receiving Hopper</t>
+          <t>Struktur Sipil</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4.1.2</t>
+          <t>3.6.1</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -3667,14 +3667,14 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Storage Bin</t>
+          <t>Platform kerja</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4.1.3</t>
+          <t>3.6.2</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -3687,14 +3687,14 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Pelletizer</t>
+          <t>Railing</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4.1.4</t>
+          <t>3.6.3</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -3707,34 +3707,34 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Conveyor</t>
+          <t>Tangga</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.6.4</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Rotary Kiln</t>
+          <t>Atap</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>3.6.5</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -3747,54 +3747,54 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Rotary Kiln</t>
+          <t>Dinding</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4.2.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Burner – Rotary Kiln</t>
+          <t>Sistem Proteksi Kebakaran</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.7.1</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Sistem Flame Oven</t>
+          <t>Pompa Hydrant / Fire Pump</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4.3.1</t>
+          <t>3.7.2</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -3807,14 +3807,14 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tanur Flame Oven</t>
+          <t>Water / Hydrant</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>3.7.3</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -3827,54 +3827,54 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Prisma Pot</t>
+          <t>Motor Pump Hydrant</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>3.7.4</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Sistem Penanganan Gas Buang dan Debu</t>
+          <t>Diesel Pump</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4.4.1</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Seattle Bawah Tanur</t>
+          <t>Perkakas dan Alat Ukur Workshop</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4.4.2</t>
+          <t>3.8.1</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Seattle Atas Tanur</t>
+          <t>Lifting Tools / Peralatan Alat Berat Workshop</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4.4.3</t>
+          <t>3.8.2</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3907,54 +3907,54 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Dust Collector</t>
+          <t>Alat Ukur Maintenance / Peralatan Kelistrikan Workshop</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4.4.4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Bag House</t>
+          <t>Area Peleburan Sekunder / Dust Recovery</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4.4.5</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Blower Hisap</t>
+          <t>Sistem Penerimaan, Penyimpanan, dan Pelletizing</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4.4.6</t>
+          <t>4.1.1</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3967,34 +3967,34 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Stack / Cerobong</t>
+          <t>Dust Receiving Hopper</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.1.2</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Sistem Kelistrikan, Kontrol, Instrumentasi, dan Interlock</t>
+          <t>Storage Bin</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4.5.1</t>
+          <t>4.1.3</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4007,34 +4007,34 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Panel Electrical</t>
+          <t>Pelletizer</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.1.4</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Area QC</t>
+          <t>Conveyor</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Lab. Analisis</t>
+          <t>Rotary Kiln</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4067,14 +4067,14 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ICP-OES</t>
+          <t>Rotary Kiln</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5.1.2</t>
+          <t>4.2.2</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4087,14 +4087,14 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>XRF</t>
+          <t>Burner – Rotary Kiln</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5.1.3</t>
+          <t>4.2.3</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4107,94 +4107,94 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Mikroskop</t>
+          <t>Motor Gearbox</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5.1.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Timbangan Laboratorium</t>
+          <t>Sistem Flame Oven</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.3.1</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Area Preparasi dan Konsentrasi Bijih</t>
+          <t>Tanur Flame Oven</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Sistem Konsentrasi Bijih</t>
+          <t>Prisma Pot</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Air Table</t>
+          <t>Sistem Penanganan Gas Buang dan Debu</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>4.4.1</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4207,54 +4207,54 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>High Tension Separator (HTS)</t>
+          <t>Seattle Bawah Tanur</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.4.2</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Gas Handling Tanur Reverberatory</t>
+          <t>Seattle Atas Tanur</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.4.3</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Gas Handling Tanur Reverb</t>
+          <t>Dust Collector</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>7.1.1</t>
+          <t>4.4.4</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4267,14 +4267,14 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Skin Cooler - DCS Tanur Reverb</t>
+          <t>Bag House</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>7.1.2</t>
+          <t>4.4.5</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4287,14 +4287,14 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Bag Filter - DCS Tanur Reverb</t>
+          <t>Blower Hisap</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>7.1.3</t>
+          <t>4.4.6</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4307,134 +4307,134 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ID Fan - DCS Tanur Reverb</t>
+          <t>Stack / Cerobong</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>7.1.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Cerobong - DCS Tanur Reverb</t>
+          <t>Sistem Kelistrikan, Kontrol, Instrumentasi, dan Interlock</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4.5.1</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Area Kompresor / Udara Bertekanan</t>
+          <t>Panel Electrical</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Kompressor</t>
+          <t>Area QC</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8.1.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Distribution Board</t>
+          <t>Lab. Analisis</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Gas Handling dan Utilitas Penunjang (Registrasi Lapangan)</t>
+          <t>ICP-OES</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.1.2</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Peralatan Penunjang (Registrasi Lapangan)</t>
+          <t>XRF</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>9.1.1</t>
+          <t>5.1.3</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Water / Hydrant</t>
+          <t>Mikroskop</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>5.1.4</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -4467,54 +4467,54 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Water Circulation</t>
+          <t>Timbangan Laboratorium</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>9.1.3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Trafo Step Up 20 kV</t>
+          <t>Area Preparasi dan Konsentrasi Bijih</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>9.1.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Pneumatic System</t>
+          <t>Sistem Konsentrasi Bijih</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>9.1.6</t>
+          <t>6.1.1</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Motor Screw Hopper Elektroda Tanur</t>
+          <t>Air Table</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>9.1.7</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -4547,54 +4547,54 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Motor Pump Hydrant</t>
+          <t>High Tension Separator (HTS)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>9.1.8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Motor Gearbox</t>
+          <t>Gas Handling Tanur Reverberatory</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>9.1.9</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Ruang Trafo</t>
+          <t>Gas Handling Tanur Reverb</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>9.1.10</t>
+          <t>7.1.1</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -4607,14 +4607,14 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Diesel Pump</t>
+          <t>Skin Cooler - DCS Tanur Reverb</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>9.1.11</t>
+          <t>7.1.2</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -4627,14 +4627,14 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Gudang Kapur</t>
+          <t>Bag Filter - DCS Tanur Reverb</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>9.1.13</t>
+          <t>7.1.3</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -4647,94 +4647,94 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Gudang LB3</t>
+          <t>ID Fan - DCS Tanur Reverb</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.1.4</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Sistem Gas Handling, Ventilasi, dan Dust Collection</t>
+          <t>Cerobong - DCS Tanur Reverb</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>9.2.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ID Fan</t>
+          <t>Area dan Bangunan Umum</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>9.2.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Exhaust Fan</t>
+          <t>Bangunan</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>8.1.1</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Kompresor dan Hydrant</t>
+          <t>Pos Jaga / Area Genset</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>9.3.1</t>
+          <t>8.1.2</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -4747,34 +4747,34 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Jockey Pump</t>
+          <t>Area Peleburan / Tanur</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>9.3.2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Mesin Compressor Sullair</t>
+          <t>Bangunan dan Gedung Pabrik</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -4787,14 +4787,14 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Cooling System</t>
+          <t>Bangunan</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>9.4.1</t>
+          <t>9.1.1</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -4807,34 +4807,34 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Water Instalasi</t>
+          <t>Blower Vacuum</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.1.2</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Panel Furnace Tegangan Rendah</t>
+          <t>Bangunan Crusher</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>9.9.1</t>
+          <t>9.1.3</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -4847,54 +4847,54 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Panel Furnace Tegangan Rendah</t>
+          <t>Gedung Antrasit, Workshop, dan Gudang Pasir</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9.1.4</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Area dan Bangunan Umum</t>
+          <t>Area Bahan Bakar / Gedung HTS MS</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.1.5</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Bangunan</t>
+          <t>Gedung Komposisi</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>11.1.1</t>
+          <t>9.1.6</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -4907,14 +4907,14 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Pos Jaga / Area Genset</t>
+          <t>Gedung Musholla</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>11.1.2</t>
+          <t>9.1.7</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -4927,54 +4927,54 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Area Peleburan / Tanur</t>
+          <t>Gedung Office</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9.1.8</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Bangunan dan Gedung Pabrik</t>
+          <t>Gedung Rotary Kiln &amp; Flame Oven</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.1.9</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Bangunan</t>
+          <t>Gedung Timbangan</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>12.1.1</t>
+          <t>9.1.10</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -4987,14 +4987,14 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Blower Vacuum</t>
+          <t>Gudang Pasir</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>12.1.2</t>
+          <t>9.1.11</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5007,14 +5007,14 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Bangunan Crusher</t>
+          <t>Gudang Sparepart</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>12.1.3</t>
+          <t>9.1.12</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5027,14 +5027,14 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Gedung Antrasit, Workshop, dan Gudang Pasir</t>
+          <t>Laboratorium</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>12.1.4</t>
+          <t>9.1.13</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5047,14 +5047,14 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Area Bahan Bakar / Gedung HTS MS</t>
+          <t>Gedung Produksi</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>12.1.5</t>
+          <t>9.1.14</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5067,14 +5067,14 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Gedung Komposisi</t>
+          <t>Gedung Crystallizer</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>12.1.6</t>
+          <t>9.1.15</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5087,14 +5087,14 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Gedung Musholla</t>
+          <t>Gedung Ruang Pompa</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>12.1.7</t>
+          <t>9.1.16</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5107,14 +5107,14 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Gedung Office</t>
+          <t>Gudang Kapur</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>12.1.8</t>
+          <t>9.1.17</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5127,54 +5127,54 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Gedung Rotary Kiln &amp; Flame Oven</t>
+          <t>Gudang LB3</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>12.1.9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Gedung Timbangan</t>
+          <t>Bangunan Workshop dan Rumah Peralatan</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>12.1.10</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Gudang Pasir</t>
+          <t>Bangunan</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>12.1.11</t>
+          <t>10.1.1</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5187,14 +5187,14 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Gudang Sparepart</t>
+          <t>Workshop Teknik</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>12.1.12</t>
+          <t>10.1.2</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5207,14 +5207,14 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Laboratorium</t>
+          <t>Rumah Parkir Alat Berat</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>12.1.13</t>
+          <t>10.1.3</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5227,14 +5227,14 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Gedung Produksi</t>
+          <t>Workshop Tanur Listrik</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>12.1.14</t>
+          <t>10.1.4</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5247,14 +5247,14 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Gedung Crystallizer</t>
+          <t>Rumah Kompresor</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>12.1.15</t>
+          <t>10.1.5</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5267,94 +5267,94 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Gedung Ruang Pompa</t>
+          <t>Rumah Cooling System</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10.1.6</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Sistem / Area</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Bangunan Workshop dan Rumah Peralatan</t>
+          <t>Workshop Listrik</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.1.8</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Sub-sistem</t>
+          <t>Komponen / Peralatan</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Bangunan</t>
+          <t>Rumah Baghouse</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>13.1.1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sistem / Area</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Workshop Teknik</t>
+          <t>Struktur dan Bangunan Tanur / Pemurnian</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>13.1.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Komponen / Peralatan</t>
+          <t>Sub-sistem</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Rumah Parkir Alat Berat</t>
+          <t>Bangunan</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>13.1.3</t>
+          <t>11.1.1</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -5367,14 +5367,14 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Workshop Tanur Listrik</t>
+          <t>Rumah Mainflue</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.2</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -5387,14 +5387,14 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Rumah Kompresor</t>
+          <t>Struktur Fixed Tanur</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>13.1.5</t>
+          <t>11.1.3</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Rumah Cooling System</t>
+          <t>Struktur Fixed Pemurnian</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>13.1.6</t>
+          <t>11.1.4</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -5427,207 +5427,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Workshop Listrik</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>13.1.8</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>3</v>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Komponen / Peralatan</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>Rumah Baghouse</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>1</v>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Sistem / Area</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Struktur dan Bangunan Tanur / Pemurnian</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>2</v>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Sub-sistem</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Bangunan</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>14.1.1</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>3</v>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Komponen / Peralatan</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Rumah Mainflue</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>14.1.2</t>
-        </is>
-      </c>
-      <c r="B256" t="n">
-        <v>3</v>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Komponen / Peralatan</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>Struktur Fixed Tanur</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>14.1.3</t>
-        </is>
-      </c>
-      <c r="B257" t="n">
-        <v>3</v>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Komponen / Peralatan</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Struktur Fixed Pemurnian</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>14.1.4</t>
-        </is>
-      </c>
-      <c r="B258" t="n">
-        <v>3</v>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Komponen / Peralatan</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
           <t>Gedung Refining</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B259" t="n">
-        <v>1</v>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Sistem / Area</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Area Genset dan Power House</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>2</v>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Sub-sistem</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Genset dan Power House</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>16.1.1</t>
-        </is>
-      </c>
-      <c r="B261" t="n">
-        <v>3</v>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Komponen / Peralatan</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Panel Battery</t>
         </is>
       </c>
     </row>
